--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/conductor_grid.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/conductor_grid.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRID" sheetId="1" r:id="R68c0232dc2924e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRID" sheetId="1" r:id="R50d3837b835c4618"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,7 +467,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D5" s="36" t="str">
-        <x:v>flag for mesh type: 0 = fixed and uniform; 1 = fixed refined; 3 = adapted with initial refinement; - 1 from file; in this case the z coordinates of the conductor components must be exactly the same for each conudctor component objets.                                                                     </x:v>
+        <x:v>Flag used to select the mesh type: 0 = fixed and uniform; 1 = fixed and refined; 3 = adaptive with initial refinement; -1 = read from file. In the latter case, the z coordinates must be identical for all conductor components.</x:v>
       </x:c>
       <x:c r="E5" s="35" t="n">
         <x:v>1</x:v>
